--- a/data/bonds/CZBonds10YR.xlsx
+++ b/data/bonds/CZBonds10YR.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CZGB10YR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CZBond" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,26 +429,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Trade Price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Log_return</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Return</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Z-Score</t>
         </is>
@@ -454,336 +463,276 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
-        <v>2005</v>
+      <c r="B2" s="2" t="n">
+        <v>40908</v>
       </c>
       <c r="C2" t="n">
-        <v>3.571101167315175</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>105.2022</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2011</v>
+      </c>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
-        <v>2006</v>
+      <c r="B3" s="2" t="n">
+        <v>41274</v>
       </c>
       <c r="C3" t="n">
-        <v>3.771857692307692</v>
+        <v>119.1358</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0562</v>
+        <v>2012</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.09859313653905281</v>
+        <v>0.1244</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.561243358030492</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
-        <v>2007</v>
+      <c r="B4" s="2" t="n">
+        <v>41639</v>
       </c>
       <c r="C4" t="n">
-        <v>4.339367816091954</v>
+        <v>118.7647</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1505</v>
+        <v>2013</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07856995917554041</v>
+        <v>-0.0031</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.3032720003782842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
-        <v>2008</v>
+      <c r="B5" s="2" t="n">
+        <v>42004</v>
       </c>
       <c r="C5" t="n">
-        <v>4.644961389961391</v>
+        <v>130.7183</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0704</v>
+        <v>2014</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.07191534269867927</v>
+        <v>0.0959</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.144469336739119</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
-        <v>2009</v>
+      <c r="B6" s="2" t="n">
+        <v>42369</v>
       </c>
       <c r="C6" t="n">
-        <v>4.748509578544062</v>
+        <v>133.3922</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0223</v>
+        <v>2015</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1622816725382544</v>
+        <v>0.0202</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03745904158975099</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
-        <v>2010</v>
+      <c r="B7" s="2" t="n">
+        <v>42735</v>
       </c>
       <c r="C7" t="n">
-        <v>3.869465384615385</v>
+        <v>135.4594</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1851</v>
+        <v>2016</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5519277600377945</v>
+        <v>0.0154</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.03273447778563821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
-        <v>2011</v>
+      <c r="B8" s="2" t="n">
+        <v>43100</v>
       </c>
       <c r="C8" t="n">
-        <v>3.769918918918919</v>
+        <v>128.1937</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0257</v>
+        <v>2017</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2524601305902213</v>
+        <v>-0.0551</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.063701793611668</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
-        <v>2012</v>
+      <c r="B9" s="2" t="n">
+        <v>43465</v>
       </c>
       <c r="C9" t="n">
-        <v>2.824638461538461</v>
+        <v>127.2155</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2507</v>
+        <v>2018</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.675171652708816</v>
+        <v>-0.0077</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.3705407897796989</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
-        <v>2013</v>
+      <c r="B10" s="2" t="n">
+        <v>43830</v>
       </c>
       <c r="C10" t="n">
-        <v>2.105880308880309</v>
+        <v>132.1609</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2545</v>
+        <v>2019</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.68231078063793</v>
+        <v>0.0381</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2992223742604734</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
-        <v>2014</v>
+      <c r="B11" s="2" t="n">
+        <v>44196</v>
       </c>
       <c r="C11" t="n">
-        <v>1.560509652509653</v>
+        <v>138.3412</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.259</v>
+        <v>2020</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6907650110803019</v>
+        <v>0.0457</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4103621132715062</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
-        <v>2015</v>
+      <c r="B12" s="2" t="n">
+        <v>44561</v>
       </c>
       <c r="C12" t="n">
-        <v>0.698073359073359</v>
+        <v>124.7198</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5527</v>
+        <v>2021</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.242544451285774</v>
+        <v>-0.1037</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.774411177287483</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
-        <v>2016</v>
+      <c r="B13" s="2" t="n">
+        <v>44926</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4427088122605364</v>
+        <v>114.5424</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3658</v>
+        <v>2022</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8914120802459282</v>
+        <v>-0.0851</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.50241128970785</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
-        <v>2017</v>
+      <c r="B14" s="2" t="n">
+        <v>45291</v>
       </c>
       <c r="C14" t="n">
-        <v>1.055007843137255</v>
+        <v>129.072</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3831</v>
+        <v>2023</v>
       </c>
       <c r="E14" t="n">
-        <v>2.394277613235006</v>
+        <v>0.1194</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.488125108681128</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
-        <v>2018</v>
+      <c r="B15" s="2" t="n">
+        <v>45657</v>
       </c>
       <c r="C15" t="n">
-        <v>2.023360465116279</v>
+        <v>132.3222</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9179</v>
+        <v>2024</v>
       </c>
       <c r="E15" t="n">
-        <v>1.520298057281361</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.610953488372093</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-0.2038</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-0.5870597843205401</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.183796812749004</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-0.2652</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-0.7024130619120142</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.970693227091634</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.6647</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.044606691057235</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4.451758754863814</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.259</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2.16112872481315</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4.524160784313726</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.0163</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0.1735539797947503</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C21" t="n">
-        <v>4.0127265625</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-0.113</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0.416472201172236</v>
+        <v>0.0249</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1061901959781529</v>
       </c>
     </row>
   </sheetData>
